--- a/Generators/Experiment with utility data leak/utility results/11. online shopping/TRTR_TSTR_results_merged.xlsx
+++ b/Generators/Experiment with utility data leak/utility results/11. online shopping/TRTR_TSTR_results_merged.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quality_Metrics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="TRTR_Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="All_Comparisons" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CTGAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="CopulaGAN" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="TVAE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="GaussianCopula" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="WGAN_GP" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="CTABGAN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality_Metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTGAN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopulaGAN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVAE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaussianCopula" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WGAN_GP" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTABGAN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,13 +28,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +56,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,21 +436,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Generator</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Quality_Score</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -527,6 +541,36 @@
         <v>0.01041483875451275</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9151970007980958</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.7816998382320683</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
@@ -547,152 +591,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -1815,6 +1859,2578 @@
       <c r="AD11" t="inlineStr">
         <is>
           <t>CTABGAN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TRTR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean ± SD)_TRTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean ± SD)_TRTR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean ± SD)_TRTR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean ± SD)_TRTR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TSTR</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean ± SD)_TSTR</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean ± SD)_TSTR</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean ± SD)_TSTR</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean ± SD)_TSTR</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Drop</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_Increase</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_Increase</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_Increase</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.96703485720025</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.009886887544862492</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.000789990466811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.799753642096517</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.422592655947136</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3827311412260999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6782799356050803</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.118521187870707</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.9670 ± 0.0099</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6.0008 ± 1.7998</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2.4226 ± 0.3827</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.6783 ± 0.1185</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>-3.13158525121493</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.9719635197786921</v>
+      </c>
+      <c r="P2" t="n">
+        <v>752.0906422537591</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>176.9307961448023</v>
+      </c>
+      <c r="R2" t="n">
+        <v>27.25149809888621</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.239769131033985</v>
+      </c>
+      <c r="T2" t="n">
+        <v>21.45726375543547</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.340641055584552</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-3.1316 ± 0.9720</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>752.0906 ± 176.9308</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>27.2515 ± 3.2398</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>21.4573 ± 3.3406</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.09862010841518</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>746.0898522632923</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>24.82890544293907</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>20.77898381983039</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9661616005407936</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.01052308345007085</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.159752742516977</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.915563181983579</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.453057844989738</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3975759209834858</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8192481728838844</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.114797286109724</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.9662 ± 0.0105</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6.1598 ± 1.9156</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2.4531 ± 0.3976</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.8192 ± 0.1148</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>-2.991046137871288</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9209748561154636</v>
+      </c>
+      <c r="P3" t="n">
+        <v>726.507689079717</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>167.6491053480648</v>
+      </c>
+      <c r="R3" t="n">
+        <v>26.79099761260255</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.118072054124564</v>
+      </c>
+      <c r="T3" t="n">
+        <v>21.11524040539529</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.243497185465211</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>-2.9910 ± 0.9210</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>726.5077 ± 167.6491</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>26.7910 ± 3.1181</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>21.1152 ± 3.2435</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.957207738412081</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>720.3479363372001</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>24.33793976761282</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>20.29599223251141</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9647218288625945</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.009708581145068921</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.42184071609496</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.767295743593935</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.510698495824568</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3624511908277557</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.064757753809357</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09600491372405284</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.9647 ± 0.0097</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6.4218 ± 1.7673</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.5107 ± 0.3625</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.0648 ± 0.0960</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>-1.990014038137779</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.8748573601053579</v>
+      </c>
+      <c r="P4" t="n">
+        <v>544.2854114239877</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>159.2541346323628</v>
+      </c>
+      <c r="R4" t="n">
+        <v>23.12201546952297</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.275805592374336</v>
+      </c>
+      <c r="T4" t="n">
+        <v>18.4525371272879</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.220297788392502</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>-1.9900 ± 0.8749</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>544.2854 ± 159.2541</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>23.1220 ± 3.2758</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>18.4525 ± 3.2203</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.954735867000373</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>537.8635707078928</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>20.6113169736984</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>17.38777937347854</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9615736542104131</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.01190219757591056</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.994916799999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.166609394412335</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.612633440819578</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4334144845952289</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7495700000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1429597830005193</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.9616 ± 0.0119</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6.9949 ± 2.1666</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2.6126 ± 0.4334</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.7496 ± 0.1430</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>-3.1443472172404</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.262691243751043</v>
+      </c>
+      <c r="P5" t="n">
+        <v>754.4137590820258</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>229.8532429414748</v>
+      </c>
+      <c r="R5" t="n">
+        <v>27.15059727707431</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4.379095109488381</v>
+      </c>
+      <c r="T5" t="n">
+        <v>23.13347425773229</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.312584847809734</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>-3.1443 ± 1.2627</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>754.4138 ± 229.8532</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>27.1506 ± 4.3791</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>23.1335 ± 4.3126</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.105920871450813</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>747.4188422820257</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>24.53796383625474</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>22.38390425773229</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9601139270929011</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.009455266559465283</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.260637350000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.721183774992327</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.676441844373093</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3287964647159847</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.170585</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.09081241058724665</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.9601 ± 0.0095</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7.2606 ± 1.7212</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2.6764 ± 0.3288</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.1706 ± 0.0908</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.2707143245791125</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3019666717503647</v>
+      </c>
+      <c r="P6" t="n">
+        <v>231.313719646164</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>54.96832191207457</v>
+      </c>
+      <c r="R6" t="n">
+        <v>15.12343948587845</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.698135501443507</v>
+      </c>
+      <c r="T6" t="n">
+        <v>12.27851591742439</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.511047863179217</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>-0.2707 ± 0.3020</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>231.3137 ± 54.9683</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>15.1234 ± 1.6981</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>12.2785 ± 1.5110</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.230828251672014</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>224.053082296164</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12.44699764150536</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11.10793091742439</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9575962481665545</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.009033371028941308</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.718941522750131</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.644384275230716</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.763255883840669</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3043361503521589</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.483688736346123</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.08750368216312245</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.9576 ± 0.0090</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7.7189 ± 1.6444</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2.7633 ± 0.3043</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.4837 ± 0.0875</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>-1.436627802015564</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.7676179452608881</v>
+      </c>
+      <c r="P7" t="n">
+        <v>443.5500799632219</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>139.7328720947986</v>
+      </c>
+      <c r="R7" t="n">
+        <v>20.8521606135396</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.115815875028186</v>
+      </c>
+      <c r="T7" t="n">
+        <v>16.74186303117308</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.106406022702509</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-1.4366 ± 0.7676</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>443.5501 ± 139.7329</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>20.8522 ± 3.1158</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>16.7419 ± 3.1064</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.394224050182118</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>435.8311384404718</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>18.08890472969893</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>15.25817429482695</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9509021371784675</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01822821593718078</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.9375</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.318162351195144</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.944048021742569</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5478049588774642</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9005000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2422515909820477</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.9509 ± 0.0182</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>8.9375 ± 3.3182</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2.9440 ± 0.5478</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.9005 ± 0.2423</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>-4.15500039256798</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.152141922604883</v>
+      </c>
+      <c r="P8" t="n">
+        <v>938.3874034608768</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>209.7294635962262</v>
+      </c>
+      <c r="R8" t="n">
+        <v>30.45612372770172</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.466014512985086</v>
+      </c>
+      <c r="T8" t="n">
+        <v>26.94907441849131</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.619567700619649</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>-4.1550 ± 1.1521</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>938.3874 ± 209.7295</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>30.4561 ± 3.4660</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>26.9491 ± 3.6196</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.105902529746448</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>929.4499034608768</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>27.51207570595915</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>26.04857441849131</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9373910577204072</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01023920250178061</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11.39698124250031</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.863887083890135</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.365533160079335</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2792207229390072</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.509196149449409</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09729243726129425</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.9374 ± 0.0102</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>11.3970 ± 1.8639</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3.3655 ± 0.2792</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2.5092 ± 0.0973</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.1657414241796274</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.1405420990768231</v>
+      </c>
+      <c r="P9" t="n">
+        <v>212.205040705684</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>25.58349668019004</v>
+      </c>
+      <c r="R9" t="n">
+        <v>14.54453901613591</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.8572731405673527</v>
+      </c>
+      <c r="T9" t="n">
+        <v>11.96103308880095</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.7643135335054652</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>-0.1657 ± 0.1405</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>212.2050 ± 25.5835</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>14.5445 ± 0.8573</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>11.9610 ± 0.7643</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.103132481900035</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>200.8080594631836</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11.17900585605657</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.451836939351537</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.07196925416294936</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.06483273859728131</v>
+      </c>
+      <c r="D10" t="n">
+        <v>168.93352</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11.80178867091294</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12.99020631182109</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4571165379291493</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.244</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.353538933892405</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0720 ± 0.0648</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>168.9335 ± 11.8018</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>12.9902 ± 0.4571</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10.2440 ± 0.3535</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>-1.367162847234439</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.3309360130131837</v>
+      </c>
+      <c r="P10" t="n">
+        <v>430.9050685986128</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>60.24173856724709</v>
+      </c>
+      <c r="R10" t="n">
+        <v>20.71208616077394</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.45852111830562</v>
+      </c>
+      <c r="T10" t="n">
+        <v>16.93711915063446</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.23581673041134</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-1.3672 ± 0.3309</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>430.9051 ± 60.2417</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>20.7121 ± 1.4585</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>16.9371 ± 1.2358</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.439132101397389</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>261.9715485986128</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.721879848952851</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.693119150634455</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.002408587447309108</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.02357682734688778</v>
+      </c>
+      <c r="D11" t="n">
+        <v>181.5959542291815</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.291793619994307</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.47493004361626</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1571077083812699</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.56628583900171</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.03472214492441093</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.0024 ± 0.0236</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>181.5960 ± 4.2918</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>13.4749 ± 0.1571</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>10.5663 ± 0.0347</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.880183320445404</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.6391715164818224</v>
+      </c>
+      <c r="P11" t="n">
+        <v>524.2924426272868</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>116.3512034998587</v>
+      </c>
+      <c r="R11" t="n">
+        <v>22.73092530451607</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.905450324208341</v>
+      </c>
+      <c r="T11" t="n">
+        <v>18.91238950400693</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.479289875088127</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-1.8802 ± 0.6392</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>524.2924 ± 116.3512</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>22.7309 ± 2.9055</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>18.9124 ± 2.4793</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.882591907892713</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>342.6964883981053</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>9.255995260899809</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.346103665005218</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TRTR</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TRTR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TRTR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean ± SD)_TRTR</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean ± SD)_TRTR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean ± SD)_TRTR</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean ± SD)_TRTR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>R2 Std_TSTR</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>MSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Mean_TSTR</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>MAE Std_TSTR</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2 (Mean ± SD)_TSTR</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>MSE (Mean ± SD)_TSTR</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (Mean ± SD)_TSTR</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MAE (Mean ± SD)_TSTR</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Drop</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_Increase</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_Increase</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_Increase</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.96703485720025</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.009886887544862492</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6.000789990466811</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.799753642096517</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.422592655947136</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3827311412260999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6782799356050803</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.118521187870707</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.9670 ± 0.0099</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6.0008 ± 1.7998</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2.4226 ± 0.3827</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.6783 ± 0.1185</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7019383322995771</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.02162127359382211</v>
+      </c>
+      <c r="P2" t="n">
+        <v>54.25747684284585</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.935815565887256</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7.361610814719602</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2670061494282602</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.541260016497858</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.2217959471706185</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.7019 ± 0.0216</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>54.2575 ± 3.9358</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>7.3616 ± 0.2670</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>5.5413 ± 0.2218</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.2650965249006728</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>48.25668685237903</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.939018158772465</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>4.862980080892777</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9661616005407936</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.01052308345007085</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6.159752742516977</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.915563181983579</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.453057844989738</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3975759209834858</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8192481728838844</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.114797286109724</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.9662 ± 0.0105</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6.1598 ± 1.9156</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2.4531 ± 0.3976</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.8192 ± 0.1148</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7157184145720373</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01774965409858884</v>
+      </c>
+      <c r="P3" t="n">
+        <v>51.74902783442791</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.231047634044157</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7.190537724359013</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2240909264805588</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.371527868087583</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1443371510878914</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.7157 ± 0.0177</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>51.7490 ± 3.2310</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7.1905 ± 0.2241</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>5.3715 ± 0.1443</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.2504431859687563</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>45.58927509191093</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4.737479879369275</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.552279695203699</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9647218288625945</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.009708581145068921</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.42184071609496</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.767295743593935</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.510698495824568</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3624511908277557</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.064757753809357</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.09600491372405284</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.9647 ± 0.0097</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6.4218 ± 1.7673</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2.5107 ± 0.3625</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.0648 ± 0.0960</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7266043358331613</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01580006486300442</v>
+      </c>
+      <c r="P4" t="n">
+        <v>49.76741568921196</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.87615532729809</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7.051943091067431</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2041631416247996</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5.235480352191415</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.142398932786957</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.7266 ± 0.0158</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>49.7674 ± 2.8762</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7.0519 ± 0.2042</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>5.2355 ± 0.1424</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.2381174930294332</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>43.345574973117</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4.541244595242863</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.170722598382057</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9615736542104131</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.01190219757591056</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.994916799999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.166609394412335</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.612633440819578</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4334144845952289</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7495700000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1429597830005193</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.9616 ± 0.0119</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6.9949 ± 2.1666</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2.6126 ± 0.4334</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.7496 ± 0.1430</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8011517313771387</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01598833103435491</v>
+      </c>
+      <c r="P5" t="n">
+        <v>36.19722526980136</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.910426246840172</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6.011943724314117</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2443993214245068</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.315407899602715</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1542424289421693</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.8012 ± 0.0160</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>36.1972 ± 2.9104</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>6.0119 ± 0.2444</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>4.3154 ± 0.1542</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.1604219228332744</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>29.20230846980137</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.399310283494539</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.565837899602714</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9601139270929011</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.009455266559465283</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.260637350000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.721183774992327</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.676441844373093</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3287964647159847</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.170585</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.09081241058724665</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.9601 ± 0.0095</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7.2606 ± 1.7212</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2.6764 ± 0.3288</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1.1706 ± 0.0908</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7967706196969889</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01220628918005095</v>
+      </c>
+      <c r="P6" t="n">
+        <v>36.99473830583045</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.221964527117062</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6.079892919950042</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1814766216097566</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.425145154230533</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1426480954279392</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.7968 ± 0.0122</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>36.9947 ± 2.2220</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6.0799 ± 0.1815</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>4.4251 ± 0.1426</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.1633433073959122</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>29.73410095583045</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.403451075576949</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.254560154230533</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9575962481665545</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.009033371028941308</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.718941522750131</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.644384275230716</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.763255883840669</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3043361503521589</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.483688736346123</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.08750368216312245</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.9576 ± 0.0090</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7.7189 ± 1.6444</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2.7633 ± 0.3043</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1.4837 ± 0.0875</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.7336663200903332</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01338811439878369</v>
+      </c>
+      <c r="P7" t="n">
+        <v>48.48189162214824</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.437097371713949</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6.96089948199563</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1756575699770252</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.140477999314884</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1216190690565361</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.7337 ± 0.0134</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>48.4819 ± 2.4371</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6.9609 ± 0.1757</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>5.1405 ± 0.1216</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.2239299280762214</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>40.76295009939811</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.19764359815496</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.656789262968761</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9509021371784675</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01822821593718078</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8.9375</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.318162351195144</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.944048021742569</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5478049588774642</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9005000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2422515909820477</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.9509 ± 0.0182</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>8.9375 ± 3.3182</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2.9440 ± 0.5478</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.9005 ± 0.2423</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7521745469747004</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.02282015217233429</v>
+      </c>
+      <c r="P8" t="n">
+        <v>45.1127576461886</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.154052708599573</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.710174773955079</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3096811068852633</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.841391412232327</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2207940873092793</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.7522 ± 0.0228</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>45.1128 ± 4.1541</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6.7102 ± 0.3097</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4.8414 ± 0.2208</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.1987275902037671</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>36.1752576461886</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.76612675221251</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.940891412232327</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9373910577204072</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.01023920250178061</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11.39698124250031</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.863887083890135</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.365533160079335</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2792207229390072</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.509196149449409</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09729243726129425</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.9374 ± 0.0102</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>11.3970 ± 1.8639</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3.3655 ± 0.2792</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2.5092 ± 0.0973</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7778052076999966</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.00734393648420379</v>
+      </c>
+      <c r="P9" t="n">
+        <v>40.44709569945573</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.336849071540149</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6.359035142283231</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1041780455790589</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.621621734619151</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.08133685569639022</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.7778 ± 0.0073</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>40.4471 ± 1.3368</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6.3590 ± 0.1042</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>4.6216 ± 0.0813</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.1595858500204106</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>29.05011445695542</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.993501982203896</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.112425585169742</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.07196925416294936</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.06483273859728131</v>
+      </c>
+      <c r="D10" t="n">
+        <v>168.93352</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11.80178867091294</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12.99020631182109</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4571165379291493</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.244</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.353538933892405</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0720 ± 0.0648</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>168.9335 ± 11.8018</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>12.9902 ± 0.4571</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>10.2440 ± 0.3535</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.02227662369471935</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.04379280464615802</v>
+      </c>
+      <c r="P10" t="n">
+        <v>177.9792881717059</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.971796918080583</v>
+      </c>
+      <c r="R10" t="n">
+        <v>13.33786560577655</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2993126458124923</v>
+      </c>
+      <c r="T10" t="n">
+        <v>10.28113195563924</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2694834381400431</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.0223 ± 0.0438</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>177.9793 ± 7.9718</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>13.3379 ± 0.2993</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>10.2811 ± 0.2695</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.04969263046823</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9.045768171705959</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.3476592939554539</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.03713195563923932</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.002408587447309108</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.02357682734688778</v>
+      </c>
+      <c r="D11" t="n">
+        <v>181.5959542291815</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.291793619994307</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13.47493004361626</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1571077083812699</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.56628583900171</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.03472214492441093</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.0024 ± 0.0236</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>181.5960 ± 4.2918</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>13.4749 ± 0.1571</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>10.5663 ± 0.0347</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.03465571810072408</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.02596755589038559</v>
+      </c>
+      <c r="P11" t="n">
+        <v>188.3429328510344</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.726988455972808</v>
+      </c>
+      <c r="R11" t="n">
+        <v>13.72284141297964</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1717763573347237</v>
+      </c>
+      <c r="T11" t="n">
+        <v>10.54838829629279</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.05670150836445242</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-0.0347 ± 0.0260</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>188.3429 ± 4.7270</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>13.7228 ± 0.1718</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>10.5484 ± 0.0567</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.03706430554803319</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.74697862185289</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.2479113693633863</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.01789754270892452</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -1833,67 +4449,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)</t>
         </is>
@@ -2420,156 +5036,156 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -9292,6 +11908,2246 @@
       <c r="AD61" t="inlineStr">
         <is>
           <t>CTABGAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.96703485720025</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.009886887544862492</v>
+      </c>
+      <c r="D62" t="n">
+        <v>6.000789990466811</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.799753642096517</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.422592655947136</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.3827311412260999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.6782799356050803</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.118521187870707</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.9670 ± 0.0099</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>6.0008 ± 1.7998</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2.4226 ± 0.3827</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>0.6783 ± 0.1185</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>-3.13158525121493</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.9719635197786921</v>
+      </c>
+      <c r="P62" t="n">
+        <v>752.0906422537591</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>176.9307961448023</v>
+      </c>
+      <c r="R62" t="n">
+        <v>27.25149809888621</v>
+      </c>
+      <c r="S62" t="n">
+        <v>3.239769131033985</v>
+      </c>
+      <c r="T62" t="n">
+        <v>21.45726375543547</v>
+      </c>
+      <c r="U62" t="n">
+        <v>3.340641055584552</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>-3.1316 ± 0.9720</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>752.0906 ± 176.9308</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>27.2515 ± 3.2398</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>21.4573 ± 3.3406</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>4.09862010841518</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>746.0898522632923</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>24.82890544293907</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>20.77898381983039</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.9661616005407936</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.01052308345007085</v>
+      </c>
+      <c r="D63" t="n">
+        <v>6.159752742516977</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.915563181983579</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.453057844989738</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.3975759209834858</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.8192481728838844</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.114797286109724</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.9662 ± 0.0105</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>6.1598 ± 1.9156</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2.4531 ± 0.3976</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>0.8192 ± 0.1148</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>-2.991046137871288</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.9209748561154636</v>
+      </c>
+      <c r="P63" t="n">
+        <v>726.507689079717</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>167.6491053480648</v>
+      </c>
+      <c r="R63" t="n">
+        <v>26.79099761260255</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3.118072054124564</v>
+      </c>
+      <c r="T63" t="n">
+        <v>21.11524040539529</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3.243497185465211</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>-2.9910 ± 0.9210</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>726.5077 ± 167.6491</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26.7910 ± 3.1181</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>21.1152 ± 3.2435</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>3.957207738412081</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>720.3479363372001</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>24.33793976761282</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>20.29599223251141</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.9647218288625945</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.009708581145068921</v>
+      </c>
+      <c r="D64" t="n">
+        <v>6.42184071609496</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.767295743593935</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.510698495824568</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.3624511908277557</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.064757753809357</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.09600491372405284</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.9647 ± 0.0097</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>6.4218 ± 1.7673</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2.5107 ± 0.3625</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1.0648 ± 0.0960</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>-1.990014038137779</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.8748573601053579</v>
+      </c>
+      <c r="P64" t="n">
+        <v>544.2854114239877</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>159.2541346323628</v>
+      </c>
+      <c r="R64" t="n">
+        <v>23.12201546952297</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3.275805592374336</v>
+      </c>
+      <c r="T64" t="n">
+        <v>18.4525371272879</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3.220297788392502</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>-1.9900 ± 0.8749</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>544.2854 ± 159.2541</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>23.1220 ± 3.2758</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>18.4525 ± 3.2203</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>2.954735867000373</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>537.8635707078928</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>20.6113169736984</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>17.38777937347854</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.9615736542104131</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.01190219757591056</v>
+      </c>
+      <c r="D65" t="n">
+        <v>6.994916799999999</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.166609394412335</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2.612633440819578</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.4334144845952289</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.7495700000000001</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.1429597830005193</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.9616 ± 0.0119</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>6.9949 ± 2.1666</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2.6126 ± 0.4334</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>0.7496 ± 0.1430</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>-3.1443472172404</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.262691243751043</v>
+      </c>
+      <c r="P65" t="n">
+        <v>754.4137590820258</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>229.8532429414748</v>
+      </c>
+      <c r="R65" t="n">
+        <v>27.15059727707431</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4.379095109488381</v>
+      </c>
+      <c r="T65" t="n">
+        <v>23.13347425773229</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4.312584847809734</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>-3.1443 ± 1.2627</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>754.4138 ± 229.8532</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>27.1506 ± 4.3791</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>23.1335 ± 4.3126</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>4.105920871450813</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>747.4188422820257</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>24.53796383625474</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>22.38390425773229</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.9601139270929011</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.009455266559465283</v>
+      </c>
+      <c r="D66" t="n">
+        <v>7.260637350000001</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.721183774992327</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.676441844373093</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.3287964647159847</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.170585</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.09081241058724665</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.9601 ± 0.0095</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>7.2606 ± 1.7212</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2.6764 ± 0.3288</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>1.1706 ± 0.0908</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>-0.2707143245791125</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.3019666717503647</v>
+      </c>
+      <c r="P66" t="n">
+        <v>231.313719646164</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>54.96832191207457</v>
+      </c>
+      <c r="R66" t="n">
+        <v>15.12343948587845</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1.698135501443507</v>
+      </c>
+      <c r="T66" t="n">
+        <v>12.27851591742439</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.511047863179217</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>-0.2707 ± 0.3020</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>231.3137 ± 54.9683</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>15.1234 ± 1.6981</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>12.2785 ± 1.5110</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>1.230828251672014</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>224.053082296164</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>12.44699764150536</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>11.10793091742439</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.9575962481665545</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.009033371028941308</v>
+      </c>
+      <c r="D67" t="n">
+        <v>7.718941522750131</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.644384275230716</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.763255883840669</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.3043361503521589</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.483688736346123</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.08750368216312245</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.9576 ± 0.0090</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>7.7189 ± 1.6444</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2.7633 ± 0.3043</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1.4837 ± 0.0875</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>-1.436627802015564</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.7676179452608881</v>
+      </c>
+      <c r="P67" t="n">
+        <v>443.5500799632219</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>139.7328720947986</v>
+      </c>
+      <c r="R67" t="n">
+        <v>20.8521606135396</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3.115815875028186</v>
+      </c>
+      <c r="T67" t="n">
+        <v>16.74186303117308</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3.106406022702509</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>-1.4366 ± 0.7676</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>443.5501 ± 139.7329</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>20.8522 ± 3.1158</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>16.7419 ± 3.1064</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>2.394224050182118</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>435.8311384404718</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>18.08890472969893</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>15.25817429482695</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.9509021371784675</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.01822821593718078</v>
+      </c>
+      <c r="D68" t="n">
+        <v>8.9375</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3.318162351195144</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2.944048021742569</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.5478049588774642</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.9005000000000001</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.2422515909820477</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0.9509 ± 0.0182</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>8.9375 ± 3.3182</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2.9440 ± 0.5478</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>0.9005 ± 0.2423</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>-4.15500039256798</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1.152141922604883</v>
+      </c>
+      <c r="P68" t="n">
+        <v>938.3874034608768</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>209.7294635962262</v>
+      </c>
+      <c r="R68" t="n">
+        <v>30.45612372770172</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3.466014512985086</v>
+      </c>
+      <c r="T68" t="n">
+        <v>26.94907441849131</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3.619567700619649</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>-4.1550 ± 1.1521</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>938.3874 ± 209.7295</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>30.4561 ± 3.4660</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>26.9491 ± 3.6196</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>5.105902529746448</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>929.4499034608768</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>27.51207570595915</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>26.04857441849131</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.9373910577204072</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.01023920250178061</v>
+      </c>
+      <c r="D69" t="n">
+        <v>11.39698124250031</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.863887083890135</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3.365533160079335</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.2792207229390072</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2.509196149449409</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.09729243726129425</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0.9374 ± 0.0102</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>11.3970 ± 1.8639</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>3.3655 ± 0.2792</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2.5092 ± 0.0973</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>-0.1657414241796274</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.1405420990768231</v>
+      </c>
+      <c r="P69" t="n">
+        <v>212.205040705684</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>25.58349668019004</v>
+      </c>
+      <c r="R69" t="n">
+        <v>14.54453901613591</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.8572731405673527</v>
+      </c>
+      <c r="T69" t="n">
+        <v>11.96103308880095</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0.7643135335054652</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>-0.1657 ± 0.1405</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>212.2050 ± 25.5835</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>14.5445 ± 0.8573</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>11.9610 ± 0.7643</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>1.103132481900035</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>200.8080594631836</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>11.17900585605657</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>9.451836939351537</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.07196925416294936</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.06483273859728131</v>
+      </c>
+      <c r="D70" t="n">
+        <v>168.93352</v>
+      </c>
+      <c r="E70" t="n">
+        <v>11.80178867091294</v>
+      </c>
+      <c r="F70" t="n">
+        <v>12.99020631182109</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.4571165379291493</v>
+      </c>
+      <c r="H70" t="n">
+        <v>10.244</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.353538933892405</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0.0720 ± 0.0648</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>168.9335 ± 11.8018</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>12.9902 ± 0.4571</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>10.2440 ± 0.3535</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>-1.367162847234439</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.3309360130131837</v>
+      </c>
+      <c r="P70" t="n">
+        <v>430.9050685986128</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>60.24173856724709</v>
+      </c>
+      <c r="R70" t="n">
+        <v>20.71208616077394</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1.45852111830562</v>
+      </c>
+      <c r="T70" t="n">
+        <v>16.93711915063446</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1.23581673041134</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>-1.3672 ± 0.3309</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>430.9051 ± 60.2417</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>20.7121 ± 1.4585</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>16.9371 ± 1.2358</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>1.439132101397389</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>261.9715485986128</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>7.721879848952851</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>6.693119150634455</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.002408587447309108</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.02357682734688778</v>
+      </c>
+      <c r="D71" t="n">
+        <v>181.5959542291815</v>
+      </c>
+      <c r="E71" t="n">
+        <v>4.291793619994307</v>
+      </c>
+      <c r="F71" t="n">
+        <v>13.47493004361626</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.1571077083812699</v>
+      </c>
+      <c r="H71" t="n">
+        <v>10.56628583900171</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.03472214492441093</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0.0024 ± 0.0236</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>181.5960 ± 4.2918</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>13.4749 ± 0.1571</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>10.5663 ± 0.0347</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>-1.880183320445404</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.6391715164818224</v>
+      </c>
+      <c r="P71" t="n">
+        <v>524.2924426272868</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>116.3512034998587</v>
+      </c>
+      <c r="R71" t="n">
+        <v>22.73092530451607</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2.905450324208341</v>
+      </c>
+      <c r="T71" t="n">
+        <v>18.91238950400693</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2.479289875088127</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>-1.8802 ± 0.6392</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>524.2924 ± 116.3512</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>22.7309 ± 2.9055</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>18.9124 ± 2.4793</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.882591907892713</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>342.6964883981053</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>9.255995260899809</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>8.346103665005218</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>LinearRegression</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.96703485720025</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.009886887544862492</v>
+      </c>
+      <c r="D72" t="n">
+        <v>6.000789990466811</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.799753642096517</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2.422592655947136</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.3827311412260999</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.6782799356050803</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.118521187870707</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0.9670 ± 0.0099</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>6.0008 ± 1.7998</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2.4226 ± 0.3827</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>0.6783 ± 0.1185</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0.7019383322995771</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.02162127359382211</v>
+      </c>
+      <c r="P72" t="n">
+        <v>54.25747684284585</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>3.935815565887256</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7.361610814719602</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0.2670061494282602</v>
+      </c>
+      <c r="T72" t="n">
+        <v>5.541260016497858</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0.2217959471706185</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0.7019 ± 0.0216</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>54.2575 ± 3.9358</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>7.3616 ± 0.2670</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>5.5413 ± 0.2218</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.2650965249006728</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>48.25668685237903</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>4.939018158772465</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>4.862980080892777</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.9661616005407936</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.01052308345007085</v>
+      </c>
+      <c r="D73" t="n">
+        <v>6.159752742516977</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.915563181983579</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.453057844989738</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.3975759209834858</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.8192481728838844</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.114797286109724</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0.9662 ± 0.0105</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>6.1598 ± 1.9156</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2.4531 ± 0.3976</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>0.8192 ± 0.1148</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0.7157184145720373</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.01774965409858884</v>
+      </c>
+      <c r="P73" t="n">
+        <v>51.74902783442791</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>3.231047634044157</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7.190537724359013</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.2240909264805588</v>
+      </c>
+      <c r="T73" t="n">
+        <v>5.371527868087583</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0.1443371510878914</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0.7157 ± 0.0177</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>51.7490 ± 3.2310</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>7.1905 ± 0.2241</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>5.3715 ± 0.1443</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.2504431859687563</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>45.58927509191093</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>4.737479879369275</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>4.552279695203699</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ElasticNet</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.9647218288625945</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.009708581145068921</v>
+      </c>
+      <c r="D74" t="n">
+        <v>6.42184071609496</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.767295743593935</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.510698495824568</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.3624511908277557</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1.064757753809357</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09600491372405284</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0.9647 ± 0.0097</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>6.4218 ± 1.7673</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2.5107 ± 0.3625</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1.0648 ± 0.0960</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0.7266043358331613</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.01580006486300442</v>
+      </c>
+      <c r="P74" t="n">
+        <v>49.76741568921196</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2.87615532729809</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7.051943091067431</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.2041631416247996</v>
+      </c>
+      <c r="T74" t="n">
+        <v>5.235480352191415</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0.142398932786957</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0.7266 ± 0.0158</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>49.7674 ± 2.8762</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>7.0519 ± 0.2042</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>5.2355 ± 0.1424</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.2381174930294332</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>43.345574973117</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>4.541244595242863</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>4.170722598382057</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.9615736542104131</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.01190219757591056</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6.994916799999999</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.166609394412335</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.612633440819578</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.4334144845952289</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.7495700000000001</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.1429597830005193</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>0.9616 ± 0.0119</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>6.9949 ± 2.1666</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2.6126 ± 0.4334</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>0.7496 ± 0.1430</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0.8011517313771387</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.01598833103435491</v>
+      </c>
+      <c r="P75" t="n">
+        <v>36.19722526980136</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2.910426246840172</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6.011943724314117</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.2443993214245068</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4.315407899602715</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0.1542424289421693</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0.8012 ± 0.0160</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>36.1972 ± 2.9104</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>6.0119 ± 0.2444</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>4.3154 ± 0.1542</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1604219228332744</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>29.20230846980137</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.399310283494539</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.565837899602714</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.9601139270929011</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.009455266559465283</v>
+      </c>
+      <c r="D76" t="n">
+        <v>7.260637350000001</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.721183774992327</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.676441844373093</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.3287964647159847</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1.170585</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09081241058724665</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.9601 ± 0.0095</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>7.2606 ± 1.7212</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2.6764 ± 0.3288</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1.1706 ± 0.0908</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0.7967706196969889</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.01220628918005095</v>
+      </c>
+      <c r="P76" t="n">
+        <v>36.99473830583045</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.221964527117062</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6.079892919950042</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.1814766216097566</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4.425145154230533</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0.1426480954279392</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0.7968 ± 0.0122</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>36.9947 ± 2.2220</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>6.0799 ± 0.1815</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>4.4251 ± 0.1426</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.1633433073959122</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>29.73410095583045</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>3.403451075576949</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>3.254560154230533</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.9575962481665545</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.009033371028941308</v>
+      </c>
+      <c r="D77" t="n">
+        <v>7.718941522750131</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.644384275230716</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.763255883840669</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.3043361503521589</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1.483688736346123</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.08750368216312245</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>0.9576 ± 0.0090</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>7.7189 ± 1.6444</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2.7633 ± 0.3043</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1.4837 ± 0.0875</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0.7336663200903332</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.01338811439878369</v>
+      </c>
+      <c r="P77" t="n">
+        <v>48.48189162214824</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2.437097371713949</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6.96089948199563</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0.1756575699770252</v>
+      </c>
+      <c r="T77" t="n">
+        <v>5.140477999314884</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0.1216190690565361</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0.7337 ± 0.0134</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>48.4819 ± 2.4371</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>6.9609 ± 0.1757</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>5.1405 ± 0.1216</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.2239299280762214</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>40.76295009939811</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>4.19764359815496</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>3.656789262968761</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.9509021371784675</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.01822821593718078</v>
+      </c>
+      <c r="D78" t="n">
+        <v>8.9375</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3.318162351195144</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.944048021742569</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.5478049588774642</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.9005000000000001</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.2422515909820477</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>0.9509 ± 0.0182</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>8.9375 ± 3.3182</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2.9440 ± 0.5478</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>0.9005 ± 0.2423</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0.7521745469747004</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.02282015217233429</v>
+      </c>
+      <c r="P78" t="n">
+        <v>45.1127576461886</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>4.154052708599573</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6.710174773955079</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.3096811068852633</v>
+      </c>
+      <c r="T78" t="n">
+        <v>4.841391412232327</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0.2207940873092793</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0.7522 ± 0.0228</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>45.1128 ± 4.1541</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>6.7102 ± 0.3097</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>4.8414 ± 0.2208</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.1987275902037671</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>36.1752576461886</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>3.76612675221251</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>3.940891412232327</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.9373910577204072</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.01023920250178061</v>
+      </c>
+      <c r="D79" t="n">
+        <v>11.39698124250031</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.863887083890135</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3.365533160079335</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.2792207229390072</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2.509196149449409</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09729243726129425</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>0.9374 ± 0.0102</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>11.3970 ± 1.8639</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>3.3655 ± 0.2792</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2.5092 ± 0.0973</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0.7778052076999966</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.00734393648420379</v>
+      </c>
+      <c r="P79" t="n">
+        <v>40.44709569945573</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1.336849071540149</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6.359035142283231</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.1041780455790589</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4.621621734619151</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0.08133685569639022</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0.7778 ± 0.0073</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>40.4471 ± 1.3368</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>6.3590 ± 0.1042</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>4.6216 ± 0.0813</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.1595858500204106</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>29.05011445695542</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>2.993501982203896</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>2.112425585169742</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.07196925416294936</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.06483273859728131</v>
+      </c>
+      <c r="D80" t="n">
+        <v>168.93352</v>
+      </c>
+      <c r="E80" t="n">
+        <v>11.80178867091294</v>
+      </c>
+      <c r="F80" t="n">
+        <v>12.99020631182109</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.4571165379291493</v>
+      </c>
+      <c r="H80" t="n">
+        <v>10.244</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.353538933892405</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>0.0720 ± 0.0648</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>168.9335 ± 11.8018</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>12.9902 ± 0.4571</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>10.2440 ± 0.3535</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0.02227662369471935</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.04379280464615802</v>
+      </c>
+      <c r="P80" t="n">
+        <v>177.9792881717059</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>7.971796918080583</v>
+      </c>
+      <c r="R80" t="n">
+        <v>13.33786560577655</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.2993126458124923</v>
+      </c>
+      <c r="T80" t="n">
+        <v>10.28113195563924</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0.2694834381400431</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0.0223 ± 0.0438</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>177.9793 ± 7.9718</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>13.3379 ± 0.2993</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>10.2811 ± 0.2695</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.04969263046823</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>9.045768171705959</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>0.3476592939554539</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0.03713195563923932</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SVR_RBF</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.002408587447309108</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.02357682734688778</v>
+      </c>
+      <c r="D81" t="n">
+        <v>181.5959542291815</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4.291793619994307</v>
+      </c>
+      <c r="F81" t="n">
+        <v>13.47493004361626</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.1571077083812699</v>
+      </c>
+      <c r="H81" t="n">
+        <v>10.56628583900171</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.03472214492441093</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>0.0024 ± 0.0236</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>181.5960 ± 4.2918</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>13.4749 ± 0.1571</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>10.5663 ± 0.0347</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>-0.03465571810072408</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.02596755589038559</v>
+      </c>
+      <c r="P81" t="n">
+        <v>188.3429328510344</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>4.726988455972808</v>
+      </c>
+      <c r="R81" t="n">
+        <v>13.72284141297964</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0.1717763573347237</v>
+      </c>
+      <c r="T81" t="n">
+        <v>10.54838829629279</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0.05670150836445242</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>-0.0347 ± 0.0260</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>188.3429 ± 4.7270</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>13.7228 ± 0.1718</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>10.5484 ± 0.0567</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.03706430554803319</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>6.74697862185289</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0.2479113693633863</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>-0.01789754270892452</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -9306,31 +14162,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
@@ -9448,6 +14304,44 @@
       </c>
       <c r="E7" t="n">
         <v>44.29098069560222</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ForestDiffusion</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1746422738444711</v>
+      </c>
+      <c r="C8" t="n">
+        <v>31.79090153391397</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.25733469883463</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.013572110161292</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.827229590806916</v>
+      </c>
+      <c r="C9" t="n">
+        <v>514.6530422247826</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18.05209850635777</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15.77523990692865</v>
       </c>
     </row>
   </sheetData>
@@ -9465,152 +14359,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -10751,152 +15645,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -12037,152 +16931,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -13323,152 +18217,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -14609,152 +19503,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>R2 Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>R2 Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MSE Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>RMSE Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RMSE Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MAE Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAE Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>R2 (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>RMSE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAE (Mean ± SD)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R2_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MSE_Increase</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>RMSE_Increase</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAE_Increase</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
